--- a/Luban/Datas/MissilePattern.xlsx
+++ b/Luban/Datas/MissilePattern.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1951,6 +1951,266 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>level1_split_fighter_split</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>level1_split_parent_1101</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>boss_p1_slow_homing_5</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>missile_weak_homing_1002</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>main_3</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>boss_p2_lock_dash_5</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>missile_lock_dash_1003</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>main_3</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>boss_p3_split_5</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>level1_split_parent_1101</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>main_3</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/MissilePattern.xlsx
+++ b/Luban/Datas/MissilePattern.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="1" r:id="R550e0d86ff044b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="1" r:id="R875634865cf64b2d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2101,7 +2101,7 @@
         <x:v>missile_weak_homing_1002</x:v>
       </x:c>
       <x:c r="F25" t="str">
-        <x:v>left,right</x:v>
+        <x:v>left,left1,right,right1</x:v>
       </x:c>
       <x:c r="G25" t="n">
         <x:v>0</x:v>
@@ -2113,13 +2113,13 @@
         <x:v>-90</x:v>
       </x:c>
       <x:c r="J25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K25" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L25" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M25" t="n">
         <x:v>2.6</x:v>
@@ -2158,7 +2158,7 @@
         <x:v>missile_lock_dash_1003</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>left,right</x:v>
+        <x:v>left,left1,right,right1</x:v>
       </x:c>
       <x:c r="G26" t="n">
         <x:v>0</x:v>
@@ -2170,13 +2170,13 @@
         <x:v>-90</x:v>
       </x:c>
       <x:c r="J26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L26" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M26" t="n">
         <x:v>0.8</x:v>

--- a/Luban/Datas/MissilePattern.xlsx
+++ b/Luban/Datas/MissilePattern.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="1" r:id="R875634865cf64b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MissilePattern" sheetId="1" r:id="Raf8a163345924256"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2206,10 +2206,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>boss_02_p1_side_homing_3</x:v>
+        <x:v>boss_02_p1_side_homing_1</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>Fan</x:v>
+        <x:v>Aim</x:v>
       </x:c>
       <x:c r="E27" t="str">
         <x:v>missile_weak_homing_1002</x:v>
@@ -2227,13 +2227,13 @@
         <x:v>-90</x:v>
       </x:c>
       <x:c r="J27" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K27" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L27" t="n">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M27" t="n">
         <x:v>2.7</x:v>
@@ -2263,13 +2263,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>boss_02_p2_side_lock_2</x:v>
+        <x:v>boss_02_p2_side_fast_homing</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>Fan</x:v>
+        <x:v>Aim</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>missile_lock_dash_1003</x:v>
+        <x:v>missile_fast_homing_1201</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>left,right</x:v>
@@ -2284,19 +2284,19 @@
         <x:v>-90</x:v>
       </x:c>
       <x:c r="J28" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K28" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L28" t="n">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M28" t="n">
-        <x:v>1</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="N28" t="n">
-        <x:v>4.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="O28" s="7" t="b">
         <x:v>0</x:v>
@@ -2320,16 +2320,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>boss_02_p3_all_fast_homing</x:v>
+        <x:v>boss_02_p3_center_homing_burst</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>Aim</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>missile_fast_homing_1201</x:v>
+        <x:v>missile_weak_homing_1002</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>left,center,right</x:v>
+        <x:v>center</x:v>
       </x:c>
       <x:c r="G29" t="n">
         <x:v>0</x:v>
@@ -2350,7 +2350,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M29" t="n">
-        <x:v>4.2</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="N29" t="n">
         <x:v>6</x:v>
@@ -2365,68 +2365,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R29" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="S29" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
-      <x:c r="B30" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>boss_02_p3_all_fast_lock</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>Aim</x:v>
-      </x:c>
-      <x:c r="E30" t="str">
-        <x:v>missile_lock_dash_1003</x:v>
-      </x:c>
-      <x:c r="F30" t="str">
-        <x:v>left,center,right</x:v>
-      </x:c>
-      <x:c r="G30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I30" t="n">
-        <x:v>-90</x:v>
-      </x:c>
-      <x:c r="J30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M30" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="N30" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="O30" s="7" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q30" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S30" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+      <x:c r="I30"/>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
+      <x:c r="M30"/>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+      <x:c r="P30"/>
+      <x:c r="Q30"/>
+      <x:c r="R30"/>
+      <x:c r="S30"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
